--- a/datas/template_전기실_운영일지.xlsx
+++ b/datas/template_전기실_운영일지.xlsx
@@ -5,19 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\pygame\pygame\elec_room_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mariadbelecroomscada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2672221E-5C5C-4DF3-9D04-A6E487382297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CB0452-15BD-4749-B350-5A083AACA17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="2955" windowWidth="25455" windowHeight="11295" xr2:uid="{943AB7D1-EB27-49C3-9C36-555299583416}"/>
+    <workbookView xWindow="-26355" yWindow="5040" windowWidth="25455" windowHeight="11295" activeTab="1" xr2:uid="{943AB7D1-EB27-49C3-9C36-555299583416}"/>
   </bookViews>
   <sheets>
     <sheet name="전력설비_운전현황" sheetId="4" r:id="rId1"/>
     <sheet name="상세내역" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">전력설비_운전현황!$A$1:$J$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">상세내역!$A$1:$AB$57</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">전력설비_운전현황!$A$1:$J$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1658,7 +1659,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1668,9 +1669,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1690,9 +1688,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1857,6 +1852,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2521,36 +2519,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="23.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="113" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="9"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
     </row>
     <row r="3" spans="1:10" ht="25.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
       <c r="D3" s="2" t="s">
         <v>170</v>
       </c>
@@ -2564,417 +2562,417 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="82" t="s">
+      <c r="A5" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="115"/>
-      <c r="C5" s="82" t="s">
+      <c r="B5" s="114"/>
+      <c r="C5" s="81" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82" t="s">
+      <c r="D5" s="81"/>
+      <c r="E5" s="81" t="s">
         <v>174</v>
       </c>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82" t="s">
+      <c r="F5" s="81"/>
+      <c r="G5" s="81" t="s">
         <v>175</v>
       </c>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82" t="s">
+      <c r="H5" s="81"/>
+      <c r="I5" s="81" t="s">
         <v>176</v>
       </c>
-      <c r="J5" s="82"/>
+      <c r="J5" s="81"/>
     </row>
     <row r="6" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="116"/>
-      <c r="B6" s="117"/>
-      <c r="C6" s="10" t="s">
+      <c r="A6" s="115"/>
+      <c r="B6" s="116"/>
+      <c r="C6" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="9" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="82" t="s">
+      <c r="A7" s="81" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="48" t="s">
+      <c r="H7" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="48" t="s">
+      <c r="I7" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="J7" s="48" t="s">
+      <c r="J7" s="46" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="82"/>
-      <c r="B8" s="10" t="s">
+      <c r="A8" s="81"/>
+      <c r="B8" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="46" t="s">
         <v>183</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="F8" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="48" t="s">
+      <c r="G8" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="48" t="s">
+      <c r="H8" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="I8" s="48" t="s">
+      <c r="I8" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="J8" s="48" t="s">
+      <c r="J8" s="46" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="82"/>
-      <c r="B9" s="10" t="s">
+      <c r="A9" s="81"/>
+      <c r="B9" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="F9" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="G9" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="48" t="s">
+      <c r="H9" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="48" t="s">
+      <c r="I9" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="J9" s="48" t="s">
+      <c r="J9" s="46" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="82" t="s">
+      <c r="A10" s="81" t="s">
         <v>186</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="46" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="48" t="s">
+      <c r="E10" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="48" t="s">
+      <c r="F10" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="48" t="s">
+      <c r="G10" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="48" t="s">
+      <c r="H10" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="48" t="s">
+      <c r="I10" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="J10" s="48" t="s">
+      <c r="J10" s="46" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="82"/>
-      <c r="B11" s="10" t="s">
+      <c r="A11" s="81"/>
+      <c r="B11" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="46" t="s">
         <v>190</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="48" t="s">
+      <c r="E11" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="48" t="s">
+      <c r="F11" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="48" t="s">
+      <c r="G11" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="48" t="s">
+      <c r="H11" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="I11" s="48" t="s">
+      <c r="I11" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="J11" s="48" t="s">
+      <c r="J11" s="46" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="82"/>
-      <c r="B12" s="10" t="s">
+      <c r="A12" s="81"/>
+      <c r="B12" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="48" t="s">
+      <c r="F12" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="48" t="s">
+      <c r="G12" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="48" t="s">
+      <c r="H12" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="48" t="s">
+      <c r="I12" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="J12" s="48" t="s">
+      <c r="J12" s="46" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="82" t="s">
+      <c r="A13" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="46" t="s">
         <v>194</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="48" t="s">
+      <c r="E13" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="48" t="s">
+      <c r="F13" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="48" t="s">
+      <c r="G13" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="H13" s="48" t="s">
+      <c r="H13" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="I13" s="48" t="s">
+      <c r="I13" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="J13" s="48" t="s">
+      <c r="J13" s="46" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="82"/>
-      <c r="B14" s="10" t="s">
+      <c r="A14" s="81"/>
+      <c r="B14" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="46" t="s">
         <v>195</v>
       </c>
-      <c r="D14" s="48" t="s">
+      <c r="D14" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="48" t="s">
+      <c r="F14" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="48" t="s">
+      <c r="G14" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="48" t="s">
+      <c r="H14" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="I14" s="48" t="s">
+      <c r="I14" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="48" t="s">
+      <c r="J14" s="46" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="82"/>
-      <c r="B15" s="10" t="s">
+      <c r="A15" s="81"/>
+      <c r="B15" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="48" t="s">
+      <c r="E15" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="48" t="s">
+      <c r="F15" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="48" t="s">
+      <c r="G15" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="48" t="s">
+      <c r="H15" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="48" t="s">
+      <c r="I15" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="J15" s="48" t="s">
+      <c r="J15" s="46" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="46" t="s">
         <v>198</v>
       </c>
-      <c r="D16" s="48" t="s">
+      <c r="D16" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="48" t="s">
+      <c r="E16" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="48" t="s">
+      <c r="F16" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="H16" s="48" t="s">
+      <c r="H16" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="48" t="s">
+      <c r="I16" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="J16" s="48" t="s">
+      <c r="J16" s="46" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="110" t="s">
         <v>199</v>
       </c>
-      <c r="B17" s="112"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48" t="s">
+      <c r="B17" s="111"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46" t="s">
         <v>200</v>
       </c>
-      <c r="F17" s="48" t="s">
+      <c r="F17" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="G17" s="48" t="s">
+      <c r="G17" s="46" t="s">
         <v>202</v>
       </c>
-      <c r="H17" s="48" t="s">
+      <c r="H17" s="46" t="s">
         <v>203</v>
       </c>
-      <c r="I17" s="48" t="s">
+      <c r="I17" s="46" t="s">
         <v>204</v>
       </c>
-      <c r="J17" s="48" t="s">
+      <c r="J17" s="46" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="113" t="s">
+      <c r="A18" s="112" t="s">
         <v>222</v>
       </c>
-      <c r="B18" s="113"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="49" t="e">
+      <c r="B18" s="112"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="47" t="e">
         <f>+E16/1000</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F18" s="50" t="e">
+      <c r="F18" s="48" t="e">
         <f>+F16/1000</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G18" s="49" t="e">
+      <c r="G18" s="47" t="e">
         <f>+G16/1250</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H18" s="50" t="e">
+      <c r="H18" s="48" t="e">
         <f t="shared" ref="H18:J18" si="0">+H16/1250</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I18" s="49" t="e">
+      <c r="I18" s="47" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J18" s="50" t="e">
+      <c r="J18" s="48" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
@@ -2985,60 +2983,60 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="125" t="s">
+      <c r="A20" s="124" t="s">
         <v>207</v>
       </c>
-      <c r="B20" s="121"/>
-      <c r="C20" s="121" t="s">
+      <c r="B20" s="120"/>
+      <c r="C20" s="120" t="s">
         <v>208</v>
       </c>
-      <c r="D20" s="121"/>
-      <c r="E20" s="122" t="s">
+      <c r="D20" s="120"/>
+      <c r="E20" s="121" t="s">
         <v>209</v>
       </c>
-      <c r="F20" s="123"/>
-      <c r="G20" s="121" t="s">
+      <c r="F20" s="122"/>
+      <c r="G20" s="120" t="s">
         <v>210</v>
       </c>
-      <c r="H20" s="124"/>
+      <c r="H20" s="123"/>
     </row>
     <row r="21" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="126" t="s">
+      <c r="A21" s="125" t="s">
         <v>211</v>
       </c>
-      <c r="B21" s="82"/>
-      <c r="C21" s="69" t="s">
+      <c r="B21" s="81"/>
+      <c r="C21" s="68" t="s">
         <v>221</v>
       </c>
-      <c r="D21" s="69"/>
-      <c r="E21" s="83" t="s">
+      <c r="D21" s="68"/>
+      <c r="E21" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="F21" s="84"/>
-      <c r="G21" s="69" t="e">
+      <c r="F21" s="83"/>
+      <c r="G21" s="68" t="e">
         <f>E21-C21</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H21" s="119"/>
+      <c r="H21" s="118"/>
     </row>
     <row r="22" spans="1:10" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="127" t="s">
+      <c r="A22" s="126" t="s">
         <v>213</v>
       </c>
-      <c r="B22" s="128"/>
-      <c r="C22" s="118" t="s">
+      <c r="B22" s="127"/>
+      <c r="C22" s="117" t="s">
         <v>236</v>
       </c>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118" t="s">
+      <c r="D22" s="117"/>
+      <c r="E22" s="117" t="s">
         <v>237</v>
       </c>
-      <c r="F22" s="118"/>
-      <c r="G22" s="71" t="e">
+      <c r="F22" s="117"/>
+      <c r="G22" s="70" t="e">
         <f>+E22-C22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H22" s="120"/>
+      <c r="H22" s="119"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:10" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3046,344 +3044,344 @@
         <v>214</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="110" t="s">
+    <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="80"/>
-      <c r="C25" s="80" t="s">
+      <c r="B25" s="79"/>
+      <c r="C25" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80" t="s">
+      <c r="D25" s="79"/>
+      <c r="E25" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="F25" s="80"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="80" t="s">
+      <c r="F25" s="79"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="I25" s="80"/>
-      <c r="J25" s="81"/>
-    </row>
-    <row r="26" spans="1:10" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="129"/>
-      <c r="B26" s="130"/>
-      <c r="C26" s="53" t="s">
+      <c r="I25" s="79"/>
+      <c r="J25" s="80"/>
+    </row>
+    <row r="26" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="128"/>
+      <c r="B26" s="129"/>
+      <c r="C26" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="53" t="s">
+      <c r="D26" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="E26" s="53" t="s">
+      <c r="E26" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="53" t="s">
+      <c r="F26" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="53" t="s">
+      <c r="G26" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="H26" s="53" t="s">
+      <c r="H26" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="I26" s="53" t="s">
+      <c r="I26" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="J26" s="54" t="s">
+      <c r="J26" s="52" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="110" t="s">
+    <row r="27" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="109" t="s">
         <v>238</v>
       </c>
-      <c r="B27" s="80"/>
-      <c r="C27" s="57" t="s">
+      <c r="B27" s="79"/>
+      <c r="C27" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="D27" s="57" t="s">
+      <c r="D27" s="55" t="s">
         <v>240</v>
       </c>
-      <c r="E27" s="57" t="s">
+      <c r="E27" s="55" t="s">
         <v>241</v>
       </c>
-      <c r="F27" s="57" t="s">
+      <c r="F27" s="55" t="s">
         <v>242</v>
       </c>
-      <c r="G27" s="57" t="s">
+      <c r="G27" s="55" t="s">
         <v>243</v>
       </c>
-      <c r="H27" s="57" t="s">
+      <c r="H27" s="55" t="s">
         <v>244</v>
       </c>
-      <c r="I27" s="57" t="s">
+      <c r="I27" s="55" t="s">
         <v>245</v>
       </c>
-      <c r="J27" s="58" t="s">
+      <c r="J27" s="56" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="68" t="s">
+    <row r="28" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="69"/>
-      <c r="C28" s="48" t="s">
+      <c r="B28" s="68"/>
+      <c r="C28" s="46" t="s">
         <v>255</v>
       </c>
-      <c r="D28" s="48" t="s">
+      <c r="D28" s="46" t="s">
         <v>256</v>
       </c>
-      <c r="E28" s="48" t="s">
+      <c r="E28" s="46" t="s">
         <v>257</v>
       </c>
-      <c r="F28" s="48" t="s">
+      <c r="F28" s="46" t="s">
         <v>258</v>
       </c>
-      <c r="G28" s="48" t="s">
+      <c r="G28" s="46" t="s">
         <v>259</v>
       </c>
-      <c r="H28" s="48" t="s">
+      <c r="H28" s="46" t="s">
         <v>260</v>
       </c>
-      <c r="I28" s="48" t="s">
+      <c r="I28" s="46" t="s">
         <v>261</v>
       </c>
-      <c r="J28" s="59" t="s">
+      <c r="J28" s="57" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="68" t="s">
+    <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="69"/>
-      <c r="C29" s="48" t="s">
+      <c r="B29" s="68"/>
+      <c r="C29" s="46" t="s">
         <v>247</v>
       </c>
-      <c r="D29" s="48" t="s">
+      <c r="D29" s="46" t="s">
         <v>248</v>
       </c>
-      <c r="E29" s="48" t="s">
+      <c r="E29" s="46" t="s">
         <v>249</v>
       </c>
-      <c r="F29" s="48" t="s">
+      <c r="F29" s="46" t="s">
         <v>250</v>
       </c>
-      <c r="G29" s="48" t="s">
+      <c r="G29" s="46" t="s">
         <v>251</v>
       </c>
-      <c r="H29" s="48" t="s">
+      <c r="H29" s="46" t="s">
         <v>252</v>
       </c>
-      <c r="I29" s="48" t="s">
+      <c r="I29" s="46" t="s">
         <v>253</v>
       </c>
-      <c r="J29" s="59" t="s">
+      <c r="J29" s="57" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="68" t="s">
+    <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="69"/>
-      <c r="C30" s="51" t="e">
+      <c r="B30" s="68"/>
+      <c r="C30" s="49" t="e">
         <f>+C28-C29</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D30" s="51" t="e">
+      <c r="D30" s="49" t="e">
         <f t="shared" ref="D30:J30" si="1">+D28-D29</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E30" s="51" t="e">
+      <c r="E30" s="49" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F30" s="51" t="e">
+      <c r="F30" s="49" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="G30" s="51" t="e">
+      <c r="G30" s="49" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H30" s="51" t="e">
+      <c r="H30" s="49" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I30" s="51" t="e">
+      <c r="I30" s="49" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="J30" s="52" t="e">
+      <c r="J30" s="50" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="68" t="s">
+    <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="69"/>
-      <c r="C31" s="51" t="e">
+      <c r="B31" s="68"/>
+      <c r="C31" s="49" t="e">
         <f>+C30*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D31" s="51" t="e">
+      <c r="D31" s="49" t="e">
         <f>+D30*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E31" s="51" t="e">
+      <c r="E31" s="49" t="e">
         <f>E30*80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F31" s="51" t="e">
+      <c r="F31" s="49" t="e">
         <f t="shared" ref="F31:G31" si="2">F30*80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G31" s="51" t="e">
+      <c r="G31" s="49" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H31" s="51" t="e">
+      <c r="H31" s="49" t="e">
         <f>+H30</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I31" s="51" t="e">
+      <c r="I31" s="49" t="e">
         <f t="shared" ref="I31:J31" si="3">+I30</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J31" s="52" t="e">
+      <c r="J31" s="50" t="e">
         <f t="shared" si="3"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="68" t="s">
+    <row r="32" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="69"/>
-      <c r="C32" s="51" t="e">
+      <c r="B32" s="68"/>
+      <c r="C32" s="49" t="e">
         <f>(C28-C27)*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D32" s="51" t="e">
+      <c r="D32" s="49" t="e">
         <f>(D28-D27)*2400</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E32" s="51" t="e">
+      <c r="E32" s="49" t="e">
         <f>(E28-E27)*80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F32" s="51" t="e">
+      <c r="F32" s="49" t="e">
         <f t="shared" ref="F32:G32" si="4">(F28-F27)*80</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G32" s="51" t="e">
+      <c r="G32" s="49" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H32" s="51" t="e">
+      <c r="H32" s="49" t="e">
         <f>H28-H27</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I32" s="51" t="e">
+      <c r="I32" s="49" t="e">
         <f t="shared" ref="I32:J32" si="5">I28-I27</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J32" s="52" t="e">
+      <c r="J32" s="50" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="70" t="s">
+    <row r="33" spans="1:17" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="71"/>
-      <c r="C33" s="14" t="e">
+      <c r="B33" s="70"/>
+      <c r="C33" s="12" t="e">
         <f>C30/(SQRT(C30^2+D30^2*100))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="14" t="s">
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H33" s="26" t="s">
+      <c r="H33" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="I33" s="26" t="s">
+      <c r="I33" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="J33" s="27" t="s">
+      <c r="J33" s="25" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="72" t="s">
+      <c r="A34" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="73"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="55" t="s">
+      <c r="B34" s="72"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="H34" s="24" t="s">
+      <c r="H34" s="22" t="s">
         <v>263</v>
       </c>
-      <c r="I34" s="24" t="s">
+      <c r="I34" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="J34" s="25" t="s">
+      <c r="J34" s="23" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="16"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="12" t="s">
+      <c r="A35" s="14"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="I35" s="10" t="s">
+      <c r="I35" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J35" s="11" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="18"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="23" t="s">
+      <c r="A36" s="16"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="H36" s="14" t="e">
+      <c r="H36" s="12" t="e">
         <f>+H34-H35</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I36" s="14" t="e">
+      <c r="I36" s="12" t="e">
         <f t="shared" ref="I36:J36" si="6">+I34-I35</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J36" s="15" t="e">
+      <c r="J36" s="13" t="e">
         <f t="shared" si="6"/>
         <v>#VALUE!</v>
       </c>
@@ -3392,198 +3390,198 @@
       <c r="A38" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
     </row>
     <row r="39" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="77" t="s">
+      <c r="A39" s="76" t="s">
         <v>224</v>
       </c>
-      <c r="B39" s="78"/>
-      <c r="C39" s="78"/>
-      <c r="D39" s="79"/>
-      <c r="E39" s="64" t="s">
+      <c r="B39" s="77"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="62" t="s">
         <v>265</v>
       </c>
-      <c r="F39" s="63" t="s">
+      <c r="F39" s="61" t="s">
         <v>266</v>
       </c>
-      <c r="G39" s="65" t="s">
+      <c r="G39" s="63" t="s">
         <v>267</v>
       </c>
-      <c r="H39" s="66" t="s">
+      <c r="H39" s="64" t="s">
         <v>268</v>
       </c>
-      <c r="I39" s="102" t="s">
+      <c r="I39" s="101" t="s">
         <v>225</v>
       </c>
-      <c r="J39" s="103"/>
+      <c r="J39" s="102"/>
       <c r="Q39" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="104" t="s">
+      <c r="A40" s="103" t="s">
         <v>226</v>
       </c>
-      <c r="B40" s="105"/>
-      <c r="C40" s="105"/>
-      <c r="D40" s="106"/>
-      <c r="E40" s="94" t="s">
+      <c r="B40" s="104"/>
+      <c r="C40" s="104"/>
+      <c r="D40" s="105"/>
+      <c r="E40" s="93" t="s">
         <v>269</v>
       </c>
-      <c r="F40" s="99" t="s">
+      <c r="F40" s="98" t="s">
         <v>270</v>
       </c>
-      <c r="G40" s="107" t="s">
+      <c r="G40" s="106" t="s">
         <v>271</v>
       </c>
-      <c r="H40" s="67" t="s">
+      <c r="H40" s="65" t="s">
         <v>227</v>
       </c>
-      <c r="I40" s="88"/>
-      <c r="J40" s="89"/>
+      <c r="I40" s="87"/>
+      <c r="J40" s="88"/>
     </row>
     <row r="41" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="74" t="s">
+      <c r="A41" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="B41" s="75"/>
-      <c r="C41" s="75"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="95"/>
-      <c r="F41" s="100"/>
-      <c r="G41" s="108"/>
-      <c r="H41" s="61" t="s">
+      <c r="B41" s="74"/>
+      <c r="C41" s="74"/>
+      <c r="D41" s="75"/>
+      <c r="E41" s="94"/>
+      <c r="F41" s="99"/>
+      <c r="G41" s="107"/>
+      <c r="H41" s="59" t="s">
         <v>227</v>
       </c>
-      <c r="I41" s="90"/>
-      <c r="J41" s="91"/>
+      <c r="I41" s="89"/>
+      <c r="J41" s="90"/>
     </row>
     <row r="42" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="74" t="s">
+      <c r="A42" s="73" t="s">
         <v>229</v>
       </c>
-      <c r="B42" s="75"/>
-      <c r="C42" s="75"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="95"/>
-      <c r="F42" s="100"/>
-      <c r="G42" s="108"/>
-      <c r="H42" s="61" t="s">
+      <c r="B42" s="74"/>
+      <c r="C42" s="74"/>
+      <c r="D42" s="75"/>
+      <c r="E42" s="94"/>
+      <c r="F42" s="99"/>
+      <c r="G42" s="107"/>
+      <c r="H42" s="59" t="s">
         <v>227</v>
       </c>
-      <c r="I42" s="90"/>
-      <c r="J42" s="91"/>
+      <c r="I42" s="89"/>
+      <c r="J42" s="90"/>
     </row>
     <row r="43" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="74" t="s">
+      <c r="A43" s="73" t="s">
         <v>230</v>
       </c>
-      <c r="B43" s="75"/>
-      <c r="C43" s="75"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="95"/>
-      <c r="F43" s="100"/>
-      <c r="G43" s="108"/>
-      <c r="H43" s="61" t="s">
+      <c r="B43" s="74"/>
+      <c r="C43" s="74"/>
+      <c r="D43" s="75"/>
+      <c r="E43" s="94"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="107"/>
+      <c r="H43" s="59" t="s">
         <v>227</v>
       </c>
-      <c r="I43" s="90"/>
-      <c r="J43" s="91"/>
+      <c r="I43" s="89"/>
+      <c r="J43" s="90"/>
     </row>
     <row r="44" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="74" t="s">
+      <c r="A44" s="73" t="s">
         <v>231</v>
       </c>
-      <c r="B44" s="75"/>
-      <c r="C44" s="75"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="96"/>
-      <c r="F44" s="101"/>
-      <c r="G44" s="109"/>
-      <c r="H44" s="61" t="s">
+      <c r="B44" s="74"/>
+      <c r="C44" s="74"/>
+      <c r="D44" s="75"/>
+      <c r="E44" s="95"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="108"/>
+      <c r="H44" s="59" t="s">
         <v>227</v>
       </c>
-      <c r="I44" s="90"/>
-      <c r="J44" s="91"/>
+      <c r="I44" s="89"/>
+      <c r="J44" s="90"/>
     </row>
     <row r="45" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="74" t="s">
+      <c r="A45" s="73" t="s">
         <v>232</v>
       </c>
-      <c r="B45" s="75"/>
-      <c r="C45" s="75"/>
-      <c r="D45" s="76"/>
-      <c r="E45" s="97" t="s">
+      <c r="B45" s="74"/>
+      <c r="C45" s="74"/>
+      <c r="D45" s="75"/>
+      <c r="E45" s="96" t="s">
         <v>272</v>
       </c>
-      <c r="F45" s="97" t="s">
+      <c r="F45" s="96" t="s">
         <v>273</v>
       </c>
-      <c r="G45" s="97" t="s">
+      <c r="G45" s="96" t="s">
         <v>274</v>
       </c>
-      <c r="H45" s="61" t="s">
+      <c r="H45" s="59" t="s">
         <v>227</v>
       </c>
-      <c r="I45" s="90"/>
-      <c r="J45" s="91"/>
+      <c r="I45" s="89"/>
+      <c r="J45" s="90"/>
     </row>
     <row r="46" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="74" t="s">
+      <c r="A46" s="73" t="s">
         <v>233</v>
       </c>
-      <c r="B46" s="75"/>
-      <c r="C46" s="75"/>
-      <c r="D46" s="76"/>
-      <c r="E46" s="97"/>
-      <c r="F46" s="97"/>
-      <c r="G46" s="97"/>
-      <c r="H46" s="61" t="s">
+      <c r="B46" s="74"/>
+      <c r="C46" s="74"/>
+      <c r="D46" s="75"/>
+      <c r="E46" s="96"/>
+      <c r="F46" s="96"/>
+      <c r="G46" s="96"/>
+      <c r="H46" s="59" t="s">
         <v>227</v>
       </c>
-      <c r="I46" s="90"/>
-      <c r="J46" s="91"/>
+      <c r="I46" s="89"/>
+      <c r="J46" s="90"/>
     </row>
     <row r="47" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="74" t="s">
+      <c r="A47" s="73" t="s">
         <v>234</v>
       </c>
-      <c r="B47" s="75"/>
-      <c r="C47" s="75"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="97"/>
-      <c r="F47" s="97"/>
-      <c r="G47" s="97"/>
-      <c r="H47" s="61" t="s">
+      <c r="B47" s="74"/>
+      <c r="C47" s="74"/>
+      <c r="D47" s="75"/>
+      <c r="E47" s="96"/>
+      <c r="F47" s="96"/>
+      <c r="G47" s="96"/>
+      <c r="H47" s="59" t="s">
         <v>227</v>
       </c>
-      <c r="I47" s="90"/>
-      <c r="J47" s="91"/>
+      <c r="I47" s="89"/>
+      <c r="J47" s="90"/>
     </row>
     <row r="48" spans="1:17" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="85" t="s">
+      <c r="A48" s="84" t="s">
         <v>235</v>
       </c>
-      <c r="B48" s="86"/>
-      <c r="C48" s="86"/>
-      <c r="D48" s="87"/>
-      <c r="E48" s="98"/>
-      <c r="F48" s="98"/>
-      <c r="G48" s="98"/>
-      <c r="H48" s="62" t="s">
+      <c r="B48" s="85"/>
+      <c r="C48" s="85"/>
+      <c r="D48" s="86"/>
+      <c r="E48" s="97"/>
+      <c r="F48" s="97"/>
+      <c r="G48" s="97"/>
+      <c r="H48" s="60" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="92"/>
-      <c r="J48" s="93"/>
+      <c r="I48" s="91"/>
+      <c r="J48" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="61">
@@ -3686,7 +3684,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="48" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3695,7 +3693,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB58"/>
+  <dimension ref="A1:AB57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -3709,222 +3707,222 @@
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="140" t="s">
+      <c r="A4" s="139" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="144" t="s">
+      <c r="B4" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="145" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="141" t="s">
         <v>146</v>
       </c>
-      <c r="E4" s="143"/>
-      <c r="F4" s="134" t="s">
+      <c r="E4" s="142"/>
+      <c r="F4" s="133" t="s">
         <v>147</v>
       </c>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="135"/>
-      <c r="M4" s="135"/>
-      <c r="N4" s="135"/>
-      <c r="O4" s="135"/>
-      <c r="P4" s="135"/>
-      <c r="Q4" s="136"/>
-      <c r="R4" s="137" t="s">
+      <c r="G4" s="134"/>
+      <c r="H4" s="134"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="134"/>
+      <c r="K4" s="134"/>
+      <c r="L4" s="134"/>
+      <c r="M4" s="134"/>
+      <c r="N4" s="134"/>
+      <c r="O4" s="134"/>
+      <c r="P4" s="134"/>
+      <c r="Q4" s="135"/>
+      <c r="R4" s="136" t="s">
         <v>148</v>
       </c>
-      <c r="S4" s="135"/>
-      <c r="T4" s="135"/>
-      <c r="U4" s="135"/>
-      <c r="V4" s="135"/>
-      <c r="W4" s="135"/>
-      <c r="X4" s="135"/>
-      <c r="Y4" s="135"/>
-      <c r="Z4" s="135"/>
-      <c r="AA4" s="135"/>
-      <c r="AB4" s="136"/>
+      <c r="S4" s="134"/>
+      <c r="T4" s="134"/>
+      <c r="U4" s="134"/>
+      <c r="V4" s="134"/>
+      <c r="W4" s="134"/>
+      <c r="X4" s="134"/>
+      <c r="Y4" s="134"/>
+      <c r="Z4" s="134"/>
+      <c r="AA4" s="134"/>
+      <c r="AB4" s="135"/>
     </row>
     <row r="5" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="141"/>
-      <c r="B5" s="145"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="44" t="s">
+      <c r="A5" s="140"/>
+      <c r="B5" s="144"/>
+      <c r="C5" s="146"/>
+      <c r="D5" s="42" t="s">
         <v>149</v>
       </c>
-      <c r="E5" s="45" t="s">
+      <c r="E5" s="43" t="s">
         <v>150</v>
       </c>
-      <c r="F5" s="44" t="s">
+      <c r="F5" s="42" t="s">
         <v>151</v>
       </c>
-      <c r="G5" s="47" t="s">
+      <c r="G5" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="H5" s="47" t="s">
+      <c r="H5" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="I5" s="47" t="s">
+      <c r="I5" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="J5" s="47" t="s">
+      <c r="J5" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="K5" s="47" t="s">
+      <c r="K5" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="L5" s="47" t="s">
+      <c r="L5" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="M5" s="47" t="s">
+      <c r="M5" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="N5" s="47" t="s">
+      <c r="N5" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="O5" s="47" t="s">
+      <c r="O5" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="P5" s="47" t="s">
+      <c r="P5" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="Q5" s="45" t="s">
+      <c r="Q5" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="R5" s="46" t="s">
+      <c r="R5" s="44" t="s">
         <v>151</v>
       </c>
-      <c r="S5" s="47" t="s">
+      <c r="S5" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="T5" s="47" t="s">
+      <c r="T5" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="U5" s="47" t="s">
+      <c r="U5" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="V5" s="47" t="s">
+      <c r="V5" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="W5" s="47" t="s">
+      <c r="W5" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="X5" s="47" t="s">
+      <c r="X5" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="Y5" s="47" t="s">
+      <c r="Y5" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="Z5" s="47" t="s">
+      <c r="Z5" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="AA5" s="47" t="s">
+      <c r="AA5" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="AB5" s="45" t="s">
+      <c r="AB5" s="43" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" s="39">
+      <c r="A6" s="37">
         <v>0</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="H6" s="43" t="s">
+      <c r="H6" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="I6" s="43" t="s">
+      <c r="I6" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="J6" s="43" t="s">
+      <c r="J6" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="K6" s="43" t="s">
+      <c r="K6" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="L6" s="43" t="s">
+      <c r="L6" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="M6" s="43" t="s">
+      <c r="M6" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="N6" s="43" t="s">
+      <c r="N6" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="O6" s="43" t="s">
+      <c r="O6" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="P6" s="43" t="s">
+      <c r="P6" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="Q6" s="41" t="s">
+      <c r="Q6" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="R6" s="42" t="s">
+      <c r="R6" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="S6" s="43" t="s">
+      <c r="S6" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="T6" s="43" t="s">
+      <c r="T6" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="U6" s="43" t="s">
+      <c r="U6" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="V6" s="43" t="s">
+      <c r="V6" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="W6" s="43" t="s">
+      <c r="W6" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="X6" s="43" t="s">
+      <c r="X6" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="Y6" s="43" t="s">
+      <c r="Y6" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="Z6" s="43" t="s">
+      <c r="Z6" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="AA6" s="43" t="s">
+      <c r="AA6" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="AB6" s="43" t="s">
+      <c r="AB6" s="41" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A7" s="37">
+      <c r="A7" s="35">
         <v>1</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="35"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="33"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -3935,8 +3933,8 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="31"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="29"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -3949,14 +3947,14 @@
       <c r="AB7" s="1"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A8" s="37">
+      <c r="A8" s="35">
         <v>2</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="35"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="33"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -3967,8 +3965,8 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="31"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="29"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
@@ -3981,14 +3979,14 @@
       <c r="AB8" s="1"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" s="37">
+      <c r="A9" s="35">
         <v>3</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="35"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="33"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -3999,8 +3997,8 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="31"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="29"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
@@ -4013,14 +4011,14 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A10" s="37">
+      <c r="A10" s="35">
         <v>4</v>
       </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="35"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="33"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -4031,8 +4029,8 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="31"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="29"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
@@ -4045,14 +4043,14 @@
       <c r="AB10" s="1"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A11" s="37">
+      <c r="A11" s="35">
         <v>5</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="35"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="33"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -4063,8 +4061,8 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="31"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="29"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
@@ -4077,14 +4075,14 @@
       <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A12" s="37">
+      <c r="A12" s="35">
         <v>6</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="35"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="33"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -4095,8 +4093,8 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="31"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="29"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
@@ -4109,14 +4107,14 @@
       <c r="AB12" s="1"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A13" s="37">
+      <c r="A13" s="35">
         <v>7</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="35"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="33"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -4127,8 +4125,8 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="31"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="29"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
@@ -4141,14 +4139,14 @@
       <c r="AB13" s="1"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A14" s="37">
+      <c r="A14" s="35">
         <v>8</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="35"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="33"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -4159,8 +4157,8 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="31"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="29"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
@@ -4173,14 +4171,14 @@
       <c r="AB14" s="1"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A15" s="37">
+      <c r="A15" s="35">
         <v>9</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="35"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="33"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -4191,8 +4189,8 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="36"/>
-      <c r="R15" s="31"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="29"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
@@ -4205,14 +4203,14 @@
       <c r="AB15" s="1"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A16" s="37">
+      <c r="A16" s="35">
         <v>10</v>
       </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="35"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="33"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -4223,8 +4221,8 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="31"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="29"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
@@ -4237,14 +4235,14 @@
       <c r="AB16" s="1"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A17" s="37">
+      <c r="A17" s="35">
         <v>11</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="35"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="33"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -4255,8 +4253,8 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="31"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="29"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
@@ -4269,14 +4267,14 @@
       <c r="AB17" s="1"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A18" s="37">
+      <c r="A18" s="35">
         <v>12</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="35"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="33"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -4287,8 +4285,8 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="31"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="29"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
@@ -4301,14 +4299,14 @@
       <c r="AB18" s="1"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A19" s="37">
+      <c r="A19" s="35">
         <v>13</v>
       </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="35"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="33"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -4319,8 +4317,8 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="31"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="29"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
@@ -4333,14 +4331,14 @@
       <c r="AB19" s="1"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A20" s="37">
+      <c r="A20" s="35">
         <v>14</v>
       </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="35"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="33"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -4351,8 +4349,8 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="31"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="29"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
@@ -4365,14 +4363,14 @@
       <c r="AB20" s="1"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A21" s="37">
+      <c r="A21" s="35">
         <v>15</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="35"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="33"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -4383,8 +4381,8 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="31"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="29"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
@@ -4397,14 +4395,14 @@
       <c r="AB21" s="1"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A22" s="37">
+      <c r="A22" s="35">
         <v>16</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="35"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="33"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -4415,8 +4413,8 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="31"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="29"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
@@ -4429,14 +4427,14 @@
       <c r="AB22" s="1"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A23" s="37">
+      <c r="A23" s="35">
         <v>17</v>
       </c>
-      <c r="B23" s="35"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="35"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="33"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -4447,8 +4445,8 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="36"/>
-      <c r="R23" s="31"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="29"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
@@ -4461,14 +4459,14 @@
       <c r="AB23" s="1"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A24" s="37">
+      <c r="A24" s="35">
         <v>18</v>
       </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="35"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="33"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -4479,8 +4477,8 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
-      <c r="Q24" s="36"/>
-      <c r="R24" s="31"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="29"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
@@ -4493,14 +4491,14 @@
       <c r="AB24" s="1"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A25" s="37">
+      <c r="A25" s="35">
         <v>19</v>
       </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="35"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="33"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -4511,8 +4509,8 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="36"/>
-      <c r="R25" s="31"/>
+      <c r="Q25" s="34"/>
+      <c r="R25" s="29"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
@@ -4525,14 +4523,14 @@
       <c r="AB25" s="1"/>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A26" s="37">
+      <c r="A26" s="35">
         <v>20</v>
       </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="35"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="33"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -4543,8 +4541,8 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="36"/>
-      <c r="R26" s="31"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="29"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
@@ -4557,14 +4555,14 @@
       <c r="AB26" s="1"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A27" s="37">
+      <c r="A27" s="35">
         <v>21</v>
       </c>
-      <c r="B27" s="35"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="35"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="33"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -4575,8 +4573,8 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="36"/>
-      <c r="R27" s="31"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="29"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
@@ -4589,14 +4587,14 @@
       <c r="AB27" s="1"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A28" s="37">
+      <c r="A28" s="35">
         <v>22</v>
       </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="35"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="33"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -4607,8 +4605,8 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-      <c r="Q28" s="36"/>
-      <c r="R28" s="31"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="29"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
@@ -4621,26 +4619,26 @@
       <c r="AB28" s="1"/>
     </row>
     <row r="29" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="38">
+      <c r="A29" s="36">
         <v>23</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="31"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="29"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
@@ -4654,181 +4652,181 @@
     </row>
     <row r="31" spans="1:28" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A32" s="138" t="s">
+      <c r="A32" s="137" t="s">
         <v>144</v>
       </c>
-      <c r="B32" s="131" t="s">
+      <c r="B32" s="130" t="s">
         <v>166</v>
       </c>
-      <c r="C32" s="132"/>
-      <c r="D32" s="132"/>
-      <c r="E32" s="132"/>
-      <c r="F32" s="132"/>
-      <c r="G32" s="132"/>
-      <c r="H32" s="132"/>
-      <c r="I32" s="132"/>
-      <c r="J32" s="132"/>
-      <c r="K32" s="132"/>
-      <c r="L32" s="133"/>
-      <c r="M32" s="131" t="s">
+      <c r="C32" s="131"/>
+      <c r="D32" s="131"/>
+      <c r="E32" s="131"/>
+      <c r="F32" s="131"/>
+      <c r="G32" s="131"/>
+      <c r="H32" s="131"/>
+      <c r="I32" s="131"/>
+      <c r="J32" s="131"/>
+      <c r="K32" s="131"/>
+      <c r="L32" s="132"/>
+      <c r="M32" s="130" t="s">
         <v>167</v>
       </c>
-      <c r="N32" s="132"/>
-      <c r="O32" s="132"/>
-      <c r="P32" s="132"/>
-      <c r="Q32" s="132"/>
-      <c r="R32" s="132"/>
-      <c r="S32" s="132"/>
-      <c r="T32" s="132"/>
-      <c r="U32" s="132"/>
-      <c r="V32" s="132"/>
-      <c r="W32" s="133"/>
+      <c r="N32" s="131"/>
+      <c r="O32" s="131"/>
+      <c r="P32" s="131"/>
+      <c r="Q32" s="131"/>
+      <c r="R32" s="131"/>
+      <c r="S32" s="131"/>
+      <c r="T32" s="131"/>
+      <c r="U32" s="131"/>
+      <c r="V32" s="131"/>
+      <c r="W32" s="132"/>
     </row>
     <row r="33" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="139"/>
-      <c r="B33" s="32" t="s">
+      <c r="A33" s="138"/>
+      <c r="B33" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D33" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="E33" s="29" t="s">
+      <c r="E33" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="F33" s="29" t="s">
+      <c r="F33" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="G33" s="29" t="s">
+      <c r="G33" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="H33" s="29" t="s">
+      <c r="H33" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="I33" s="29" t="s">
+      <c r="I33" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="J33" s="29" t="s">
+      <c r="J33" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="K33" s="29" t="s">
+      <c r="K33" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="L33" s="30" t="s">
+      <c r="L33" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="M33" s="32" t="s">
+      <c r="M33" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="N33" s="29" t="s">
+      <c r="N33" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="O33" s="29" t="s">
+      <c r="O33" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="P33" s="29" t="s">
+      <c r="P33" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="Q33" s="29" t="s">
+      <c r="Q33" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="R33" s="29" t="s">
+      <c r="R33" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="S33" s="29" t="s">
+      <c r="S33" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="T33" s="29" t="s">
+      <c r="T33" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="U33" s="29" t="s">
+      <c r="U33" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="V33" s="29" t="s">
+      <c r="V33" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="W33" s="30" t="s">
+      <c r="W33" s="28" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A34" s="11">
+      <c r="A34" s="66">
         <v>0</v>
       </c>
-      <c r="B34" s="33" t="s">
+      <c r="B34" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D34" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="E34" s="28" t="s">
+      <c r="E34" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="F34" s="28" t="s">
+      <c r="F34" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="G34" s="28" t="s">
+      <c r="G34" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="H34" s="28" t="s">
+      <c r="H34" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="I34" s="28" t="s">
+      <c r="I34" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="J34" s="28" t="s">
+      <c r="J34" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="K34" s="28" t="s">
+      <c r="K34" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="L34" s="34" t="s">
+      <c r="L34" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="M34" s="33" t="s">
+      <c r="M34" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="N34" s="28" t="s">
+      <c r="N34" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="O34" s="28" t="s">
+      <c r="O34" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="P34" s="28" t="s">
+      <c r="P34" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="Q34" s="28" t="s">
+      <c r="Q34" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="R34" s="28" t="s">
+      <c r="R34" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="S34" s="28" t="s">
+      <c r="S34" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="T34" s="28" t="s">
+      <c r="T34" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="U34" s="28" t="s">
+      <c r="U34" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="V34" s="28" t="s">
+      <c r="V34" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="W34" s="34" t="s">
+      <c r="W34" s="32" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A35" s="3">
+      <c r="A35" s="35">
         <v>1</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B35" s="33"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -4838,8 +4836,8 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="36"/>
-      <c r="M35" s="35"/>
+      <c r="L35" s="34"/>
+      <c r="M35" s="33"/>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
@@ -4849,13 +4847,13 @@
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
-      <c r="W35" s="36"/>
+      <c r="W35" s="34"/>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
+      <c r="A36" s="35">
         <v>2</v>
       </c>
-      <c r="B36" s="35"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -4865,8 +4863,8 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="36"/>
-      <c r="M36" s="35"/>
+      <c r="L36" s="34"/>
+      <c r="M36" s="33"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
@@ -4876,13 +4874,13 @@
       <c r="T36" s="1"/>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
-      <c r="W36" s="36"/>
+      <c r="W36" s="34"/>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A37" s="3">
+      <c r="A37" s="35">
         <v>3</v>
       </c>
-      <c r="B37" s="35"/>
+      <c r="B37" s="33"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -4892,8 +4890,8 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="36"/>
-      <c r="M37" s="35"/>
+      <c r="L37" s="34"/>
+      <c r="M37" s="33"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
@@ -4903,13 +4901,13 @@
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
-      <c r="W37" s="36"/>
+      <c r="W37" s="34"/>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A38" s="3">
+      <c r="A38" s="35">
         <v>4</v>
       </c>
-      <c r="B38" s="35"/>
+      <c r="B38" s="33"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -4919,8 +4917,8 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="36"/>
-      <c r="M38" s="35"/>
+      <c r="L38" s="34"/>
+      <c r="M38" s="33"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -4930,13 +4928,13 @@
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
-      <c r="W38" s="36"/>
+      <c r="W38" s="34"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A39" s="3">
+      <c r="A39" s="35">
         <v>5</v>
       </c>
-      <c r="B39" s="35"/>
+      <c r="B39" s="33"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -4946,8 +4944,8 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="35"/>
+      <c r="L39" s="34"/>
+      <c r="M39" s="33"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
@@ -4957,13 +4955,13 @@
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
-      <c r="W39" s="36"/>
+      <c r="W39" s="34"/>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A40" s="3">
+      <c r="A40" s="35">
         <v>6</v>
       </c>
-      <c r="B40" s="35"/>
+      <c r="B40" s="33"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -4973,8 +4971,8 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="36"/>
-      <c r="M40" s="35"/>
+      <c r="L40" s="34"/>
+      <c r="M40" s="33"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
@@ -4984,13 +4982,13 @@
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
-      <c r="W40" s="36"/>
+      <c r="W40" s="34"/>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A41" s="3">
+      <c r="A41" s="35">
         <v>7</v>
       </c>
-      <c r="B41" s="35"/>
+      <c r="B41" s="33"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -5000,8 +4998,8 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="36"/>
-      <c r="M41" s="35"/>
+      <c r="L41" s="34"/>
+      <c r="M41" s="33"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
@@ -5011,13 +5009,13 @@
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
-      <c r="W41" s="36"/>
+      <c r="W41" s="34"/>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
+      <c r="A42" s="35">
         <v>8</v>
       </c>
-      <c r="B42" s="35"/>
+      <c r="B42" s="33"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -5027,8 +5025,8 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="L42" s="36"/>
-      <c r="M42" s="35"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="33"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -5038,13 +5036,13 @@
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
-      <c r="W42" s="36"/>
+      <c r="W42" s="34"/>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A43" s="3">
+      <c r="A43" s="35">
         <v>9</v>
       </c>
-      <c r="B43" s="35"/>
+      <c r="B43" s="33"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -5054,8 +5052,8 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-      <c r="L43" s="36"/>
-      <c r="M43" s="35"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="33"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
@@ -5065,13 +5063,13 @@
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
-      <c r="W43" s="36"/>
+      <c r="W43" s="34"/>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A44" s="3">
+      <c r="A44" s="35">
         <v>10</v>
       </c>
-      <c r="B44" s="35"/>
+      <c r="B44" s="33"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -5081,8 +5079,8 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
-      <c r="L44" s="36"/>
-      <c r="M44" s="35"/>
+      <c r="L44" s="34"/>
+      <c r="M44" s="33"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
@@ -5092,13 +5090,13 @@
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
-      <c r="W44" s="36"/>
+      <c r="W44" s="34"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A45" s="3">
+      <c r="A45" s="35">
         <v>11</v>
       </c>
-      <c r="B45" s="35"/>
+      <c r="B45" s="33"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -5108,8 +5106,8 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
-      <c r="L45" s="36"/>
-      <c r="M45" s="35"/>
+      <c r="L45" s="34"/>
+      <c r="M45" s="33"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
@@ -5119,13 +5117,13 @@
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
-      <c r="W45" s="36"/>
+      <c r="W45" s="34"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A46" s="3">
+      <c r="A46" s="35">
         <v>12</v>
       </c>
-      <c r="B46" s="35"/>
+      <c r="B46" s="33"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -5135,8 +5133,8 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
-      <c r="L46" s="36"/>
-      <c r="M46" s="35"/>
+      <c r="L46" s="34"/>
+      <c r="M46" s="33"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
@@ -5146,13 +5144,13 @@
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
-      <c r="W46" s="36"/>
+      <c r="W46" s="34"/>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A47" s="3">
+      <c r="A47" s="35">
         <v>13</v>
       </c>
-      <c r="B47" s="35"/>
+      <c r="B47" s="33"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -5162,8 +5160,8 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
-      <c r="L47" s="36"/>
-      <c r="M47" s="35"/>
+      <c r="L47" s="34"/>
+      <c r="M47" s="33"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -5173,13 +5171,13 @@
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
-      <c r="W47" s="36"/>
+      <c r="W47" s="34"/>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A48" s="3">
+      <c r="A48" s="35">
         <v>14</v>
       </c>
-      <c r="B48" s="35"/>
+      <c r="B48" s="33"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -5189,8 +5187,8 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="L48" s="36"/>
-      <c r="M48" s="35"/>
+      <c r="L48" s="34"/>
+      <c r="M48" s="33"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
@@ -5200,13 +5198,13 @@
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
-      <c r="W48" s="36"/>
+      <c r="W48" s="34"/>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A49" s="3">
+      <c r="A49" s="35">
         <v>15</v>
       </c>
-      <c r="B49" s="35"/>
+      <c r="B49" s="33"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -5216,8 +5214,8 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-      <c r="L49" s="36"/>
-      <c r="M49" s="35"/>
+      <c r="L49" s="34"/>
+      <c r="M49" s="33"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
@@ -5227,13 +5225,13 @@
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
-      <c r="W49" s="36"/>
+      <c r="W49" s="34"/>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A50" s="3">
+      <c r="A50" s="35">
         <v>16</v>
       </c>
-      <c r="B50" s="35"/>
+      <c r="B50" s="33"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -5243,8 +5241,8 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
-      <c r="L50" s="36"/>
-      <c r="M50" s="35"/>
+      <c r="L50" s="34"/>
+      <c r="M50" s="33"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
@@ -5254,13 +5252,13 @@
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
-      <c r="W50" s="36"/>
+      <c r="W50" s="34"/>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A51" s="3">
+      <c r="A51" s="35">
         <v>17</v>
       </c>
-      <c r="B51" s="35"/>
+      <c r="B51" s="33"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -5270,8 +5268,8 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
-      <c r="L51" s="36"/>
-      <c r="M51" s="35"/>
+      <c r="L51" s="34"/>
+      <c r="M51" s="33"/>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
@@ -5281,13 +5279,13 @@
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
-      <c r="W51" s="36"/>
+      <c r="W51" s="34"/>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A52" s="3">
+      <c r="A52" s="35">
         <v>18</v>
       </c>
-      <c r="B52" s="35"/>
+      <c r="B52" s="33"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -5297,8 +5295,8 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
-      <c r="L52" s="36"/>
-      <c r="M52" s="35"/>
+      <c r="L52" s="34"/>
+      <c r="M52" s="33"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
@@ -5308,13 +5306,13 @@
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
-      <c r="W52" s="36"/>
+      <c r="W52" s="34"/>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A53" s="3">
+      <c r="A53" s="35">
         <v>19</v>
       </c>
-      <c r="B53" s="35"/>
+      <c r="B53" s="33"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -5324,8 +5322,8 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
-      <c r="L53" s="36"/>
-      <c r="M53" s="35"/>
+      <c r="L53" s="34"/>
+      <c r="M53" s="33"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
@@ -5335,13 +5333,13 @@
       <c r="T53" s="1"/>
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
-      <c r="W53" s="36"/>
+      <c r="W53" s="34"/>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A54" s="3">
+      <c r="A54" s="35">
         <v>20</v>
       </c>
-      <c r="B54" s="35"/>
+      <c r="B54" s="33"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -5351,8 +5349,8 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
-      <c r="L54" s="36"/>
-      <c r="M54" s="35"/>
+      <c r="L54" s="34"/>
+      <c r="M54" s="33"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
@@ -5362,13 +5360,13 @@
       <c r="T54" s="1"/>
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
-      <c r="W54" s="36"/>
+      <c r="W54" s="34"/>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A55" s="3">
+      <c r="A55" s="35">
         <v>21</v>
       </c>
-      <c r="B55" s="35"/>
+      <c r="B55" s="33"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -5378,8 +5376,8 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
-      <c r="L55" s="36"/>
-      <c r="M55" s="35"/>
+      <c r="L55" s="34"/>
+      <c r="M55" s="33"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
       <c r="P55" s="1"/>
@@ -5389,13 +5387,13 @@
       <c r="T55" s="1"/>
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
-      <c r="W55" s="36"/>
+      <c r="W55" s="34"/>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A56" s="3">
+      <c r="A56" s="35">
         <v>22</v>
       </c>
-      <c r="B56" s="35"/>
+      <c r="B56" s="33"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -5405,8 +5403,8 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
-      <c r="L56" s="36"/>
-      <c r="M56" s="35"/>
+      <c r="L56" s="34"/>
+      <c r="M56" s="33"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
       <c r="P56" s="1"/>
@@ -5416,61 +5414,34 @@
       <c r="T56" s="1"/>
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
-      <c r="W56" s="36"/>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A57" s="3">
-        <v>22</v>
-      </c>
-      <c r="B57" s="35"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="36"/>
-      <c r="M57" s="35"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="1"/>
-      <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="1"/>
-      <c r="V57" s="1"/>
-      <c r="W57" s="36"/>
-    </row>
-    <row r="58" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="3">
+      <c r="W56" s="34"/>
+    </row>
+    <row r="57" spans="1:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="36">
         <v>23</v>
       </c>
-      <c r="B58" s="7"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="9"/>
-      <c r="M58" s="7"/>
-      <c r="N58" s="8"/>
-      <c r="O58" s="8"/>
-      <c r="P58" s="8"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
-      <c r="T58" s="8"/>
-      <c r="U58" s="8"/>
-      <c r="V58" s="8"/>
-      <c r="W58" s="9"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="7"/>
+      <c r="O57" s="7"/>
+      <c r="P57" s="7"/>
+      <c r="Q57" s="7"/>
+      <c r="R57" s="7"/>
+      <c r="S57" s="7"/>
+      <c r="T57" s="7"/>
+      <c r="U57" s="7"/>
+      <c r="V57" s="7"/>
+      <c r="W57" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="9">
